--- a/longitudinal/data_processing_elements_longitudinal-SHR.xlsx
+++ b/longitudinal/data_processing_elements_longitudinal-SHR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Computer\twey working files\ProPASS\SHR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{50E3AFEA-BB40-4352-8D1E-B080E5FA0F39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC12FD7E-1918-4F4B-A92A-C44E946FC571}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1620" windowWidth="29040" windowHeight="15720" xr2:uid="{183527E9-C397-49D1-929F-7CE96446A080}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{183527E9-C397-49D1-929F-7CE96446A080}"/>
   </bookViews>
   <sheets>
     <sheet name="Processing elements" sheetId="4" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1346" uniqueCount="458">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1346" uniqueCount="457">
   <si>
     <t>index</t>
   </si>
@@ -135,9 +135,6 @@
   </si>
   <si>
     <t>Study identifier</t>
-  </si>
-  <si>
-    <t>SHARE</t>
   </si>
   <si>
     <t>adm_dataset_id</t>
@@ -956,9 +953,6 @@
   </si>
   <si>
     <t>Montreal Cognitive Assessment (MoCA) score</t>
-  </si>
-  <si>
-    <t>SHARE_follow_up_1</t>
   </si>
   <si>
     <t>SHR_Followup_1</t>
@@ -1704,6 +1698,9 @@
   </si>
   <si>
     <t>paste(int_year, int_month, "15", sep = "-")</t>
+  </si>
+  <si>
+    <t>"SHR"</t>
   </si>
 </sst>
 </file>
@@ -2256,7 +2253,7 @@
         <v>26</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>27</v>
@@ -2265,7 +2262,7 @@
         <v>28</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L2" s="2" t="s">
         <v>11</v>
@@ -2294,13 +2291,13 @@
         <v>26</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>11</v>
@@ -2312,7 +2309,7 @@
         <v>29</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>32</v>
+        <v>456</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.35">
@@ -2320,22 +2317,22 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="E4" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>6</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L4" s="3" t="s">
         <v>11</v>
@@ -2347,7 +2344,7 @@
         <v>29</v>
       </c>
       <c r="O4" s="4" t="s">
-        <v>297</v>
+        <v>456</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.35">
@@ -2355,22 +2352,22 @@
         <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>37</v>
-      </c>
       <c r="E5" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>6</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>11</v>
@@ -2379,7 +2376,7 @@
         <v>15</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O5" s="1">
         <v>2</v>
@@ -2390,31 +2387,31 @@
         <v>4</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="E6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F6" s="1" t="s">
+      <c r="H6" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="K6" s="1" t="s">
         <v>298</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>452</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>300</v>
       </c>
       <c r="L6" s="1" t="s">
         <v>11</v>
@@ -2426,7 +2423,7 @@
         <v>18</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="29" x14ac:dyDescent="0.35">
@@ -2434,31 +2431,31 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>46</v>
-      </c>
       <c r="H7" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L7" s="1" t="s">
         <v>11</v>
@@ -2470,7 +2467,7 @@
         <v>17</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="29" x14ac:dyDescent="0.35">
@@ -2478,28 +2475,28 @@
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="E8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="G8" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="G8" s="1" t="s">
+      <c r="H8" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="H8" s="1" t="s">
-        <v>51</v>
-      </c>
       <c r="I8" s="1" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L8" s="1" t="s">
         <v>11</v>
@@ -2511,7 +2508,7 @@
         <v>18</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="174" x14ac:dyDescent="0.35">
@@ -2519,31 +2516,31 @@
         <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="E9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="G9" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>56</v>
-      </c>
       <c r="H9" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L9" s="1" t="s">
         <v>11</v>
@@ -2555,7 +2552,7 @@
         <v>17</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="174" x14ac:dyDescent="0.35">
@@ -2563,31 +2560,31 @@
         <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>59</v>
-      </c>
       <c r="E10" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L10" s="1" t="s">
         <v>11</v>
@@ -2599,7 +2596,7 @@
         <v>17</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="87" x14ac:dyDescent="0.35">
@@ -2607,31 +2604,31 @@
         <v>9</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="E11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="G11" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="E11" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>63</v>
-      </c>
       <c r="H11" s="1" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L11" s="1" t="s">
         <v>11</v>
@@ -2643,7 +2640,7 @@
         <v>17</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="P11" s="1"/>
     </row>
@@ -2652,40 +2649,40 @@
         <v>10</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="D12" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="E12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="G12" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E12" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>67</v>
-      </c>
       <c r="H12" s="1" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="L12" s="1" t="s">
         <v>12</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="N12" s="1" t="s">
         <v>12</v>
@@ -2700,28 +2697,28 @@
         <v>11</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>69</v>
-      </c>
       <c r="E13" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L13" s="1" t="s">
         <v>11</v>
@@ -2733,7 +2730,7 @@
         <v>18</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="P13" s="1"/>
     </row>
@@ -2742,28 +2739,28 @@
         <v>12</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="E14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="G14" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="E14" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>72</v>
-      </c>
       <c r="H14" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L14" s="1" t="s">
         <v>11</v>
@@ -2775,7 +2772,7 @@
         <v>19</v>
       </c>
       <c r="O14" s="15" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="P14" s="1"/>
     </row>
@@ -2784,28 +2781,28 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>74</v>
-      </c>
       <c r="E15" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H15" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I15" s="9" t="s">
         <v>325</v>
       </c>
-      <c r="I15" s="9" t="s">
-        <v>327</v>
-      </c>
       <c r="J15" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L15" s="1" t="s">
         <v>11</v>
@@ -2817,7 +2814,7 @@
         <v>17</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="P15" s="1"/>
     </row>
@@ -2826,31 +2823,31 @@
         <v>14</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="E16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="H16" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="E16" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>77</v>
-      </c>
       <c r="I16" s="9" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="L16" s="1" t="s">
         <v>11</v>
@@ -2862,10 +2859,10 @@
         <v>17</v>
       </c>
       <c r="O16" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="P16" s="1" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="17" spans="1:16" ht="101.5" x14ac:dyDescent="0.35">
@@ -2873,34 +2870,34 @@
         <v>15</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="D17" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="E17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="G17" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="E17" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="G17" s="1" t="s">
+      <c r="H17" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="H17" s="1" t="s">
+      <c r="I17" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="K17" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="I17" s="9" t="s">
-        <v>330</v>
-      </c>
-      <c r="J17" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>83</v>
       </c>
       <c r="L17" s="1" t="s">
         <v>11</v>
@@ -2912,7 +2909,7 @@
         <v>19</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="P17" s="1"/>
     </row>
@@ -2921,28 +2918,28 @@
         <v>16</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>85</v>
-      </c>
       <c r="E18" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L18" s="1" t="s">
         <v>11</v>
@@ -2954,10 +2951,10 @@
         <v>18</v>
       </c>
       <c r="O18" s="1" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="P18" s="1" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="19" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
@@ -2965,28 +2962,28 @@
         <v>17</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>87</v>
-      </c>
       <c r="E19" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L19" s="1" t="s">
         <v>11</v>
@@ -2998,10 +2995,10 @@
         <v>18</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="P19" s="1" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="20" spans="1:16" ht="29" x14ac:dyDescent="0.35">
@@ -3012,25 +3009,25 @@
         <v>2</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="G20" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="E20" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>89</v>
-      </c>
       <c r="H20" s="1" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L20" s="1" t="s">
         <v>11</v>
@@ -3042,7 +3039,7 @@
         <v>18</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="P20" s="1"/>
     </row>
@@ -3051,28 +3048,28 @@
         <v>19</v>
       </c>
       <c r="B21" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>91</v>
-      </c>
       <c r="E21" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L21" s="1" t="s">
         <v>11</v>
@@ -3084,7 +3081,7 @@
         <v>18</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="P21" s="1"/>
     </row>
@@ -3093,28 +3090,28 @@
         <v>20</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="E22" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="G22" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="E22" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="G22" s="1" t="s">
+      <c r="H22" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="H22" s="1" t="s">
+      <c r="I22" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="I22" s="1" t="s">
-        <v>97</v>
-      </c>
       <c r="J22" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L22" s="1" t="s">
         <v>11</v>
@@ -3126,7 +3123,7 @@
         <v>18</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="P22" s="1"/>
     </row>
@@ -3135,28 +3132,28 @@
         <v>21</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>99</v>
-      </c>
       <c r="E23" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>6</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L23" s="1" t="s">
         <v>12</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N23" s="1" t="s">
         <v>12</v>
@@ -3171,28 +3168,28 @@
         <v>22</v>
       </c>
       <c r="B24" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>101</v>
-      </c>
       <c r="E24" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>6</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L24" s="1" t="s">
         <v>12</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N24" s="1" t="s">
         <v>12</v>
@@ -3207,28 +3204,28 @@
         <v>23</v>
       </c>
       <c r="B25" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>103</v>
-      </c>
       <c r="E25" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>6</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L25" s="1" t="s">
         <v>12</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N25" s="1" t="s">
         <v>12</v>
@@ -3243,28 +3240,28 @@
         <v>24</v>
       </c>
       <c r="B26" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C26" s="2" t="s">
-        <v>105</v>
-      </c>
       <c r="E26" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>6</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L26" s="1" t="s">
         <v>12</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N26" s="1" t="s">
         <v>12</v>
@@ -3279,28 +3276,28 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>107</v>
-      </c>
       <c r="E27" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>6</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L27" s="1" t="s">
         <v>12</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N27" s="1" t="s">
         <v>12</v>
@@ -3315,28 +3312,28 @@
         <v>26</v>
       </c>
       <c r="B28" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="C28" s="2" t="s">
-        <v>109</v>
-      </c>
       <c r="E28" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>6</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L28" s="1" t="s">
         <v>12</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N28" s="1" t="s">
         <v>12</v>
@@ -3351,28 +3348,28 @@
         <v>27</v>
       </c>
       <c r="B29" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="C29" s="2" t="s">
-        <v>111</v>
-      </c>
       <c r="E29" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>6</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L29" s="1" t="s">
         <v>12</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N29" s="1" t="s">
         <v>12</v>
@@ -3387,28 +3384,28 @@
         <v>28</v>
       </c>
       <c r="B30" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="C30" s="2" t="s">
-        <v>113</v>
-      </c>
       <c r="E30" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>6</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L30" s="1" t="s">
         <v>12</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N30" s="1" t="s">
         <v>12</v>
@@ -3423,28 +3420,28 @@
         <v>29</v>
       </c>
       <c r="B31" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="C31" s="2" t="s">
-        <v>115</v>
-      </c>
       <c r="E31" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>6</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L31" s="1" t="s">
         <v>12</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N31" s="1" t="s">
         <v>12</v>
@@ -3459,28 +3456,28 @@
         <v>30</v>
       </c>
       <c r="B32" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="C32" s="2" t="s">
-        <v>117</v>
-      </c>
       <c r="E32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>6</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L32" s="1" t="s">
         <v>12</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N32" s="1" t="s">
         <v>12</v>
@@ -3495,28 +3492,28 @@
         <v>31</v>
       </c>
       <c r="B33" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C33" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="C33" s="2" t="s">
-        <v>119</v>
-      </c>
       <c r="E33" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>6</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L33" s="1" t="s">
         <v>12</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N33" s="1" t="s">
         <v>12</v>
@@ -3531,28 +3528,28 @@
         <v>32</v>
       </c>
       <c r="B34" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="C34" s="2" t="s">
-        <v>121</v>
-      </c>
       <c r="E34" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>6</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L34" s="1" t="s">
         <v>12</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N34" s="1" t="s">
         <v>12</v>
@@ -3567,28 +3564,28 @@
         <v>33</v>
       </c>
       <c r="B35" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C35" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="C35" s="2" t="s">
-        <v>123</v>
-      </c>
       <c r="E35" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>6</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L35" s="1" t="s">
         <v>12</v>
       </c>
       <c r="M35" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N35" s="1" t="s">
         <v>12</v>
@@ -3603,28 +3600,28 @@
         <v>34</v>
       </c>
       <c r="B36" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C36" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="C36" s="2" t="s">
-        <v>125</v>
-      </c>
       <c r="E36" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>6</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L36" s="1" t="s">
         <v>12</v>
       </c>
       <c r="M36" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N36" s="1" t="s">
         <v>12</v>
@@ -3639,28 +3636,28 @@
         <v>35</v>
       </c>
       <c r="B37" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C37" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="C37" s="2" t="s">
-        <v>127</v>
-      </c>
       <c r="E37" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>6</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L37" s="1" t="s">
         <v>12</v>
       </c>
       <c r="M37" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N37" s="1" t="s">
         <v>12</v>
@@ -3675,28 +3672,28 @@
         <v>36</v>
       </c>
       <c r="B38" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="C38" s="2" t="s">
-        <v>129</v>
-      </c>
       <c r="E38" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>6</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L38" s="1" t="s">
         <v>12</v>
       </c>
       <c r="M38" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N38" s="1" t="s">
         <v>12</v>
@@ -3711,28 +3708,28 @@
         <v>37</v>
       </c>
       <c r="B39" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C39" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="C39" s="2" t="s">
-        <v>131</v>
-      </c>
       <c r="E39" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>6</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L39" s="1" t="s">
         <v>12</v>
       </c>
       <c r="M39" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N39" s="1" t="s">
         <v>12</v>
@@ -3747,28 +3744,28 @@
         <v>38</v>
       </c>
       <c r="B40" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="C40" s="2" t="s">
-        <v>133</v>
-      </c>
       <c r="E40" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>6</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L40" s="1" t="s">
         <v>12</v>
       </c>
       <c r="M40" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="N40" s="1" t="s">
         <v>12</v>
@@ -3783,37 +3780,37 @@
         <v>39</v>
       </c>
       <c r="B41" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C41" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="C41" s="2" t="s">
-        <v>135</v>
-      </c>
       <c r="E41" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="L41" s="1" t="s">
         <v>12</v>
       </c>
       <c r="M41" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="N41" s="1" t="s">
         <v>12</v>
@@ -3828,28 +3825,28 @@
         <v>40</v>
       </c>
       <c r="B42" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C42" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="C42" s="2" t="s">
-        <v>137</v>
-      </c>
       <c r="E42" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>6</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L42" s="1" t="s">
         <v>12</v>
       </c>
       <c r="M42" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="N42" s="1" t="s">
         <v>12</v>
@@ -3864,37 +3861,37 @@
         <v>41</v>
       </c>
       <c r="B43" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C43" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="C43" s="2" t="s">
-        <v>139</v>
-      </c>
       <c r="E43" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="L43" s="1" t="s">
         <v>12</v>
       </c>
       <c r="M43" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="N43" s="1" t="s">
         <v>12</v>
@@ -3909,28 +3906,28 @@
         <v>42</v>
       </c>
       <c r="B44" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C44" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="C44" s="2" t="s">
-        <v>141</v>
-      </c>
       <c r="E44" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G44" s="1" t="s">
         <v>6</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L44" s="1" t="s">
         <v>12</v>
       </c>
       <c r="M44" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N44" s="1" t="s">
         <v>12</v>
@@ -3945,31 +3942,31 @@
         <v>43</v>
       </c>
       <c r="B45" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C45" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="C45" s="2" t="s">
-        <v>143</v>
-      </c>
       <c r="E45" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G45" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="I45" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="H45" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="I45" s="1" t="s">
-        <v>337</v>
-      </c>
       <c r="J45" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="L45" s="1" t="s">
         <v>11</v>
@@ -3981,7 +3978,7 @@
         <v>19</v>
       </c>
       <c r="O45" s="1" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="P45" s="1"/>
     </row>
@@ -3990,28 +3987,28 @@
         <v>44</v>
       </c>
       <c r="B46" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C46" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="C46" s="2" t="s">
-        <v>145</v>
-      </c>
       <c r="E46" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G46" s="1" t="s">
         <v>6</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L46" s="1" t="s">
         <v>12</v>
       </c>
       <c r="M46" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N46" s="1" t="s">
         <v>12</v>
@@ -4026,34 +4023,34 @@
         <v>45</v>
       </c>
       <c r="B47" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C47" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="D47" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="D47" s="1" t="s">
+      <c r="E47" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="G47" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="E47" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F47" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="G47" s="1" t="s">
-        <v>149</v>
-      </c>
       <c r="H47" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="L47" s="1" t="s">
         <v>11</v>
@@ -4065,7 +4062,7 @@
         <v>19</v>
       </c>
       <c r="O47" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P47" s="1"/>
     </row>
@@ -4074,31 +4071,31 @@
         <v>46</v>
       </c>
       <c r="B48" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C48" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="D48" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="D48" s="1" t="s">
-        <v>153</v>
-      </c>
       <c r="E48" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G48" s="1" t="s">
         <v>6</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L48" s="1" t="s">
         <v>12</v>
       </c>
       <c r="M48" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N48" s="1" t="s">
         <v>12</v>
@@ -4113,25 +4110,25 @@
         <v>47</v>
       </c>
       <c r="B49" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C49" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="E49" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="G49" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="E49" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F49" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="G49" s="1" t="s">
-        <v>156</v>
-      </c>
       <c r="H49" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L49" s="1" t="s">
         <v>11</v>
@@ -4143,7 +4140,7 @@
         <v>18</v>
       </c>
       <c r="O49" s="1" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="P49" s="1"/>
     </row>
@@ -4152,28 +4149,28 @@
         <v>48</v>
       </c>
       <c r="B50" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C50" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="C50" s="2" t="s">
-        <v>158</v>
-      </c>
       <c r="E50" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G50" s="1" t="s">
         <v>6</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L50" s="1" t="s">
         <v>12</v>
       </c>
       <c r="M50" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N50" s="1" t="s">
         <v>12</v>
@@ -4188,28 +4185,28 @@
         <v>49</v>
       </c>
       <c r="B51" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C51" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="C51" s="2" t="s">
-        <v>160</v>
-      </c>
       <c r="E51" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G51" s="1" t="s">
         <v>6</v>
       </c>
       <c r="J51" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L51" s="1" t="s">
         <v>12</v>
       </c>
       <c r="M51" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N51" s="1" t="s">
         <v>12</v>
@@ -4224,31 +4221,31 @@
         <v>50</v>
       </c>
       <c r="B52" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C52" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="C52" s="2" t="s">
-        <v>162</v>
-      </c>
       <c r="E52" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="I52" s="14" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="L52" s="1" t="s">
         <v>11</v>
@@ -4260,7 +4257,7 @@
         <v>17</v>
       </c>
       <c r="O52" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="P52" s="1"/>
     </row>
@@ -4269,28 +4266,28 @@
         <v>51</v>
       </c>
       <c r="B53" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C53" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="C53" s="2" t="s">
-        <v>164</v>
-      </c>
       <c r="E53" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G53" s="1" t="s">
         <v>6</v>
       </c>
       <c r="J53" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L53" s="1" t="s">
         <v>12</v>
       </c>
       <c r="M53" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N53" s="1" t="s">
         <v>12</v>
@@ -4305,28 +4302,28 @@
         <v>52</v>
       </c>
       <c r="B54" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C54" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="C54" s="2" t="s">
-        <v>166</v>
-      </c>
       <c r="E54" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>6</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L54" s="1" t="s">
         <v>12</v>
       </c>
       <c r="M54" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N54" s="1" t="s">
         <v>12</v>
@@ -4341,28 +4338,28 @@
         <v>53</v>
       </c>
       <c r="B55" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C55" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="C55" s="2" t="s">
-        <v>168</v>
-      </c>
       <c r="E55" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G55" s="1" t="s">
         <v>6</v>
       </c>
       <c r="J55" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L55" s="1" t="s">
         <v>12</v>
       </c>
       <c r="M55" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N55" s="1" t="s">
         <v>12</v>
@@ -4377,29 +4374,29 @@
         <v>54</v>
       </c>
       <c r="B56" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C56" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="C56" s="2" t="s">
-        <v>170</v>
-      </c>
       <c r="E56" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G56" s="1" t="s">
         <v>6</v>
       </c>
       <c r="H56" s="2"/>
       <c r="J56" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L56" s="1" t="s">
         <v>12</v>
       </c>
       <c r="M56" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="N56" s="1" t="s">
         <v>12</v>
@@ -4414,28 +4411,28 @@
         <v>55</v>
       </c>
       <c r="B57" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C57" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="C57" s="2" t="s">
-        <v>172</v>
-      </c>
       <c r="E57" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G57" s="1" t="s">
         <v>6</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L57" s="1" t="s">
         <v>12</v>
       </c>
       <c r="M57" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N57" s="1" t="s">
         <v>12</v>
@@ -4450,28 +4447,28 @@
         <v>56</v>
       </c>
       <c r="B58" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C58" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="C58" s="2" t="s">
-        <v>174</v>
-      </c>
       <c r="E58" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G58" s="1" t="s">
         <v>6</v>
       </c>
       <c r="J58" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L58" s="1" t="s">
         <v>12</v>
       </c>
       <c r="M58" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N58" s="1" t="s">
         <v>12</v>
@@ -4486,28 +4483,28 @@
         <v>57</v>
       </c>
       <c r="B59" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C59" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="C59" s="2" t="s">
-        <v>176</v>
-      </c>
       <c r="E59" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G59" s="1" t="s">
         <v>6</v>
       </c>
       <c r="J59" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L59" s="1" t="s">
         <v>12</v>
       </c>
       <c r="M59" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N59" s="1" t="s">
         <v>12</v>
@@ -4522,28 +4519,28 @@
         <v>58</v>
       </c>
       <c r="B60" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C60" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="C60" s="2" t="s">
-        <v>178</v>
-      </c>
       <c r="E60" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G60" s="1" t="s">
         <v>6</v>
       </c>
       <c r="J60" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L60" s="1" t="s">
         <v>12</v>
       </c>
       <c r="M60" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N60" s="1" t="s">
         <v>12</v>
@@ -4558,29 +4555,29 @@
         <v>59</v>
       </c>
       <c r="B61" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C61" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="C61" s="2" t="s">
-        <v>180</v>
-      </c>
       <c r="E61" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G61" s="1" t="s">
         <v>6</v>
       </c>
       <c r="H61" s="2"/>
       <c r="J61" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L61" s="1" t="s">
         <v>12</v>
       </c>
       <c r="M61" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N61" s="1" t="s">
         <v>12</v>
@@ -4595,28 +4592,28 @@
         <v>60</v>
       </c>
       <c r="B62" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C62" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="C62" s="2" t="s">
-        <v>182</v>
-      </c>
       <c r="E62" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G62" s="1" t="s">
         <v>6</v>
       </c>
       <c r="J62" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L62" s="1" t="s">
         <v>12</v>
       </c>
       <c r="M62" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N62" s="1" t="s">
         <v>12</v>
@@ -4631,37 +4628,37 @@
         <v>61</v>
       </c>
       <c r="B63" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C63" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="C63" s="2" t="s">
-        <v>184</v>
-      </c>
       <c r="E63" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="I63" s="14" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="J63" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="K63" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="L63" s="1" t="s">
         <v>12</v>
       </c>
       <c r="M63" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="N63" s="1" t="s">
         <v>12</v>
@@ -4676,28 +4673,28 @@
         <v>62</v>
       </c>
       <c r="B64" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C64" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="C64" s="2" t="s">
-        <v>186</v>
-      </c>
       <c r="E64" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G64" s="1" t="s">
         <v>6</v>
       </c>
       <c r="J64" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L64" s="1" t="s">
         <v>12</v>
       </c>
       <c r="M64" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N64" s="1" t="s">
         <v>12</v>
@@ -4712,31 +4709,31 @@
         <v>63</v>
       </c>
       <c r="B65" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C65" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="C65" s="2" t="s">
-        <v>188</v>
-      </c>
       <c r="D65" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G65" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="H65" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="I65" s="9" t="s">
         <v>340</v>
       </c>
-      <c r="H65" s="1" t="s">
-        <v>435</v>
-      </c>
-      <c r="I65" s="9" t="s">
-        <v>342</v>
-      </c>
       <c r="J65" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L65" s="1" t="s">
         <v>11</v>
@@ -4748,7 +4745,7 @@
         <v>19</v>
       </c>
       <c r="O65" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="P65" s="1"/>
     </row>
@@ -4757,28 +4754,28 @@
         <v>64</v>
       </c>
       <c r="B66" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C66" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="C66" s="2" t="s">
-        <v>190</v>
-      </c>
       <c r="E66" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G66" s="1" t="s">
         <v>6</v>
       </c>
       <c r="J66" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L66" s="1" t="s">
         <v>12</v>
       </c>
       <c r="M66" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N66" s="1" t="s">
         <v>12</v>
@@ -4793,28 +4790,28 @@
         <v>65</v>
       </c>
       <c r="B67" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C67" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="C67" s="2" t="s">
-        <v>192</v>
-      </c>
       <c r="E67" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G67" s="1" t="s">
         <v>6</v>
       </c>
       <c r="J67" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L67" s="1" t="s">
         <v>12</v>
       </c>
       <c r="M67" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N67" s="1" t="s">
         <v>12</v>
@@ -4829,31 +4826,31 @@
         <v>66</v>
       </c>
       <c r="B68" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C68" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="C68" s="2" t="s">
+      <c r="E68" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="G68" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="E68" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F68" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="G68" s="1" t="s">
+      <c r="H68" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="H68" s="1" t="s">
-        <v>196</v>
-      </c>
       <c r="I68" s="9" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="J68" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="K68" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="L68" s="1" t="s">
         <v>11</v>
@@ -4865,7 +4862,7 @@
         <v>17</v>
       </c>
       <c r="O68" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="P68" s="1"/>
     </row>
@@ -4874,34 +4871,34 @@
         <v>67</v>
       </c>
       <c r="B69" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C69" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="C69" s="2" t="s">
+      <c r="D69" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="D69" s="1" t="s">
-        <v>199</v>
-      </c>
       <c r="E69" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G69" s="16" t="s">
+        <v>435</v>
+      </c>
+      <c r="H69" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="I69" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="H69" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="I69" s="1" t="s">
-        <v>439</v>
-      </c>
       <c r="J69" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="K69" s="11" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="L69" s="1" t="s">
         <v>11</v>
@@ -4913,10 +4910,10 @@
         <v>17</v>
       </c>
       <c r="O69" s="11" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="P69" s="11" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="70" spans="1:16" ht="116" x14ac:dyDescent="0.35">
@@ -4924,34 +4921,34 @@
         <v>68</v>
       </c>
       <c r="B70" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C70" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="C70" s="2" t="s">
-        <v>201</v>
-      </c>
       <c r="D70" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G70" s="16" t="s">
+        <v>438</v>
+      </c>
+      <c r="H70" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="I70" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="H70" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="I70" s="1" t="s">
-        <v>442</v>
-      </c>
       <c r="J70" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="K70" s="1" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="L70" s="1" t="s">
         <v>11</v>
@@ -4963,7 +4960,7 @@
         <v>19</v>
       </c>
       <c r="O70" s="11" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="P70" s="1"/>
     </row>
@@ -4972,40 +4969,40 @@
         <v>69</v>
       </c>
       <c r="B71" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C71" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="C71" s="2" t="s">
-        <v>203</v>
-      </c>
       <c r="D71" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G71" s="16" t="s">
+        <v>438</v>
+      </c>
+      <c r="H71" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="I71" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="H71" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="I71" s="1" t="s">
-        <v>442</v>
-      </c>
       <c r="J71" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="K71" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="L71" s="1" t="s">
         <v>12</v>
       </c>
       <c r="M71" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="N71" s="1" t="s">
         <v>12</v>
@@ -5020,31 +5017,31 @@
         <v>70</v>
       </c>
       <c r="B72" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C72" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="C72" s="2" t="s">
-        <v>205</v>
-      </c>
       <c r="D72" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G72" s="1" t="s">
         <v>6</v>
       </c>
       <c r="J72" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L72" s="1" t="s">
         <v>12</v>
       </c>
       <c r="M72" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N72" s="1" t="s">
         <v>12</v>
@@ -5059,40 +5056,40 @@
         <v>71</v>
       </c>
       <c r="B73" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C73" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="C73" s="2" t="s">
-        <v>207</v>
-      </c>
       <c r="D73" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G73" s="16" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="J73" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="K73" s="1" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="L73" s="1" t="s">
         <v>12</v>
       </c>
       <c r="M73" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="N73" s="1" t="s">
         <v>12</v>
@@ -5107,31 +5104,31 @@
         <v>72</v>
       </c>
       <c r="B74" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="C74" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="C74" s="2" t="s">
-        <v>209</v>
-      </c>
       <c r="D74" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G74" s="1" t="s">
         <v>6</v>
       </c>
       <c r="J74" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L74" s="1" t="s">
         <v>12</v>
       </c>
       <c r="M74" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="N74" s="1" t="s">
         <v>12</v>
@@ -5146,31 +5143,31 @@
         <v>73</v>
       </c>
       <c r="B75" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C75" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="C75" s="2" t="s">
-        <v>211</v>
-      </c>
       <c r="D75" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G75" s="1" t="s">
         <v>6</v>
       </c>
       <c r="J75" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L75" s="1" t="s">
         <v>12</v>
       </c>
       <c r="M75" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="N75" s="1" t="s">
         <v>12</v>
@@ -5185,31 +5182,31 @@
         <v>74</v>
       </c>
       <c r="B76" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="C76" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="C76" s="2" t="s">
-        <v>213</v>
-      </c>
       <c r="D76" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="J76" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L76" s="1" t="s">
         <v>11</v>
@@ -5221,10 +5218,10 @@
         <v>17</v>
       </c>
       <c r="O76" s="11" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="P76" s="11" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="77" spans="1:16" ht="72.5" x14ac:dyDescent="0.35">
@@ -5232,31 +5229,31 @@
         <v>75</v>
       </c>
       <c r="B77" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C77" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="C77" s="2" t="s">
-        <v>215</v>
-      </c>
       <c r="D77" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="J77" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L77" s="1" t="s">
         <v>11</v>
@@ -5268,10 +5265,10 @@
         <v>19</v>
       </c>
       <c r="O77" s="11" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="P77" s="11" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="78" spans="1:16" ht="116" x14ac:dyDescent="0.35">
@@ -5279,34 +5276,34 @@
         <v>76</v>
       </c>
       <c r="B78" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="C78" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="C78" s="2" t="s">
+      <c r="D78" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="G78" s="16" t="s">
+        <v>444</v>
+      </c>
+      <c r="H78" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="I78" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="D78" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="E78" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F78" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="G78" s="16" t="s">
-        <v>446</v>
-      </c>
-      <c r="H78" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="I78" s="1" t="s">
-        <v>218</v>
-      </c>
       <c r="J78" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="K78" s="11" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="L78" s="1" t="s">
         <v>11</v>
@@ -5318,7 +5315,7 @@
         <v>19</v>
       </c>
       <c r="O78" s="1" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="P78" s="1"/>
     </row>
@@ -5327,31 +5324,31 @@
         <v>77</v>
       </c>
       <c r="B79" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C79" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="C79" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="E79" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G79" s="1" t="s">
         <v>6</v>
       </c>
       <c r="J79" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="K79" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="L79" s="1" t="s">
         <v>12</v>
       </c>
       <c r="M79" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="N79" s="1" t="s">
         <v>12</v>
@@ -5366,28 +5363,28 @@
         <v>78</v>
       </c>
       <c r="B80" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C80" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="C80" s="2" t="s">
-        <v>225</v>
-      </c>
       <c r="E80" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G80" s="1" t="s">
         <v>6</v>
       </c>
       <c r="J80" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L80" s="1" t="s">
         <v>12</v>
       </c>
       <c r="M80" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N80" s="1" t="s">
         <v>12</v>
@@ -5402,34 +5399,34 @@
         <v>79</v>
       </c>
       <c r="B81" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C81" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="C81" s="2" t="s">
-        <v>227</v>
-      </c>
       <c r="D81" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G81" s="16" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="J81" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="K81" s="11" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="L81" s="1" t="s">
         <v>11</v>
@@ -5441,10 +5438,10 @@
         <v>17</v>
       </c>
       <c r="O81" s="11" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="P81" s="11" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="82" spans="1:16" ht="72.5" x14ac:dyDescent="0.35">
@@ -5452,31 +5449,31 @@
         <v>80</v>
       </c>
       <c r="B82" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="C82" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="C82" s="2" t="s">
-        <v>229</v>
-      </c>
       <c r="D82" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E82" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="I82" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="J82" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L82" s="1" t="s">
         <v>11</v>
@@ -5488,10 +5485,10 @@
         <v>19</v>
       </c>
       <c r="O82" s="11" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="P82" s="11" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="83" spans="1:16" ht="72.5" x14ac:dyDescent="0.35">
@@ -5499,31 +5496,31 @@
         <v>81</v>
       </c>
       <c r="B83" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="C83" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="C83" s="2" t="s">
-        <v>231</v>
-      </c>
       <c r="D83" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E83" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I83" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="J83" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L83" s="1" t="s">
         <v>11</v>
@@ -5535,10 +5532,10 @@
         <v>19</v>
       </c>
       <c r="O83" s="11" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="P83" s="11" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="84" spans="1:16" ht="72.5" x14ac:dyDescent="0.35">
@@ -5546,31 +5543,31 @@
         <v>82</v>
       </c>
       <c r="B84" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="C84" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="C84" s="2" t="s">
-        <v>233</v>
-      </c>
       <c r="D84" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E84" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="J84" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L84" s="1" t="s">
         <v>11</v>
@@ -5582,10 +5579,10 @@
         <v>19</v>
       </c>
       <c r="O84" s="11" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="P84" s="11" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="85" spans="1:16" ht="72.5" x14ac:dyDescent="0.35">
@@ -5593,31 +5590,31 @@
         <v>83</v>
       </c>
       <c r="B85" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C85" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="C85" s="2" t="s">
-        <v>235</v>
-      </c>
       <c r="D85" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="J85" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L85" s="1" t="s">
         <v>11</v>
@@ -5629,10 +5626,10 @@
         <v>19</v>
       </c>
       <c r="O85" s="11" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="P85" s="11" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="86" spans="1:16" ht="72.5" x14ac:dyDescent="0.35">
@@ -5640,31 +5637,31 @@
         <v>84</v>
       </c>
       <c r="B86" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="C86" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="C86" s="2" t="s">
-        <v>237</v>
-      </c>
       <c r="D86" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E86" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="J86" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L86" s="1" t="s">
         <v>11</v>
@@ -5676,10 +5673,10 @@
         <v>19</v>
       </c>
       <c r="O86" s="11" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="P86" s="11" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="87" spans="1:16" ht="101.5" x14ac:dyDescent="0.35">
@@ -5687,31 +5684,31 @@
         <v>85</v>
       </c>
       <c r="B87" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="C87" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="C87" s="2" t="s">
-        <v>239</v>
-      </c>
       <c r="D87" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E87" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="J87" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L87" s="1" t="s">
         <v>11</v>
@@ -5723,10 +5720,10 @@
         <v>19</v>
       </c>
       <c r="O87" s="11" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="P87" s="11" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="88" spans="1:16" ht="72.5" x14ac:dyDescent="0.35">
@@ -5734,31 +5731,31 @@
         <v>86</v>
       </c>
       <c r="B88" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="C88" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="C88" s="2" t="s">
-        <v>241</v>
-      </c>
       <c r="D88" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E88" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="J88" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L88" s="1" t="s">
         <v>11</v>
@@ -5770,10 +5767,10 @@
         <v>19</v>
       </c>
       <c r="O88" s="11" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="P88" s="11" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="89" spans="1:16" ht="72.5" x14ac:dyDescent="0.35">
@@ -5781,31 +5778,31 @@
         <v>87</v>
       </c>
       <c r="B89" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C89" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="C89" s="2" t="s">
-        <v>243</v>
-      </c>
       <c r="D89" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E89" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="J89" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L89" s="1" t="s">
         <v>11</v>
@@ -5817,10 +5814,10 @@
         <v>19</v>
       </c>
       <c r="O89" s="11" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="P89" s="11" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="90" spans="1:16" ht="72.5" x14ac:dyDescent="0.35">
@@ -5828,31 +5825,31 @@
         <v>88</v>
       </c>
       <c r="B90" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="C90" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="C90" s="2" t="s">
-        <v>245</v>
-      </c>
       <c r="D90" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="H90" s="1" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="J90" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L90" s="1" t="s">
         <v>11</v>
@@ -5864,10 +5861,10 @@
         <v>19</v>
       </c>
       <c r="O90" s="11" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="P90" s="11" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="91" spans="1:16" ht="72.5" x14ac:dyDescent="0.35">
@@ -5875,31 +5872,31 @@
         <v>89</v>
       </c>
       <c r="B91" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="C91" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="C91" s="2" t="s">
-        <v>247</v>
-      </c>
       <c r="D91" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E91" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="H91" s="1" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="J91" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L91" s="1" t="s">
         <v>11</v>
@@ -5911,10 +5908,10 @@
         <v>19</v>
       </c>
       <c r="O91" s="11" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="P91" s="11" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="92" spans="1:16" ht="72.5" x14ac:dyDescent="0.35">
@@ -5922,31 +5919,31 @@
         <v>90</v>
       </c>
       <c r="B92" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="C92" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="C92" s="2" t="s">
-        <v>249</v>
-      </c>
       <c r="D92" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E92" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="H92" s="1" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="J92" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L92" s="1" t="s">
         <v>11</v>
@@ -5958,10 +5955,10 @@
         <v>19</v>
       </c>
       <c r="O92" s="11" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="P92" s="11" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="93" spans="1:16" ht="72.5" x14ac:dyDescent="0.35">
@@ -5969,31 +5966,31 @@
         <v>91</v>
       </c>
       <c r="B93" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C93" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="C93" s="2" t="s">
-        <v>251</v>
-      </c>
       <c r="D93" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E93" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="J93" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L93" s="1" t="s">
         <v>11</v>
@@ -6005,10 +6002,10 @@
         <v>19</v>
       </c>
       <c r="O93" s="11" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="P93" s="11" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="94" spans="1:16" ht="72.5" x14ac:dyDescent="0.35">
@@ -6016,31 +6013,31 @@
         <v>92</v>
       </c>
       <c r="B94" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="C94" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="C94" s="2" t="s">
-        <v>253</v>
-      </c>
       <c r="D94" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E94" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="J94" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L94" s="1" t="s">
         <v>11</v>
@@ -6052,10 +6049,10 @@
         <v>19</v>
       </c>
       <c r="O94" s="11" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="P94" s="11" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="95" spans="1:16" ht="72.5" x14ac:dyDescent="0.35">
@@ -6063,34 +6060,34 @@
         <v>93</v>
       </c>
       <c r="B95" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C95" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="C95" s="2" t="s">
-        <v>255</v>
-      </c>
       <c r="D95" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E95" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="J95" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="K95" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="L95" s="1" t="s">
         <v>11</v>
@@ -6102,10 +6099,10 @@
         <v>19</v>
       </c>
       <c r="O95" s="11" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="P95" s="11" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="96" spans="1:16" ht="72.5" x14ac:dyDescent="0.35">
@@ -6113,31 +6110,31 @@
         <v>94</v>
       </c>
       <c r="B96" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="C96" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="C96" s="2" t="s">
-        <v>257</v>
-      </c>
       <c r="D96" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E96" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="J96" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L96" s="1" t="s">
         <v>11</v>
@@ -6149,10 +6146,10 @@
         <v>19</v>
       </c>
       <c r="O96" s="11" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="P96" s="11" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="97" spans="1:16" ht="72.5" x14ac:dyDescent="0.35">
@@ -6160,31 +6157,31 @@
         <v>95</v>
       </c>
       <c r="B97" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="C97" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="C97" s="2" t="s">
-        <v>259</v>
-      </c>
       <c r="D97" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E97" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="J97" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L97" s="1" t="s">
         <v>11</v>
@@ -6196,10 +6193,10 @@
         <v>19</v>
       </c>
       <c r="O97" s="11" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="P97" s="11" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="98" spans="1:16" ht="72.5" x14ac:dyDescent="0.35">
@@ -6207,31 +6204,31 @@
         <v>96</v>
       </c>
       <c r="B98" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="C98" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="C98" s="2" t="s">
-        <v>261</v>
-      </c>
       <c r="D98" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="J98" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L98" s="1" t="s">
         <v>11</v>
@@ -6243,10 +6240,10 @@
         <v>19</v>
       </c>
       <c r="O98" s="11" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="P98" s="11" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="99" spans="1:16" ht="72.5" x14ac:dyDescent="0.35">
@@ -6254,31 +6251,31 @@
         <v>97</v>
       </c>
       <c r="B99" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="C99" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="C99" s="2" t="s">
-        <v>263</v>
-      </c>
       <c r="D99" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E99" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="I99" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="J99" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L99" s="1" t="s">
         <v>11</v>
@@ -6290,10 +6287,10 @@
         <v>19</v>
       </c>
       <c r="O99" s="11" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="P99" s="11" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="100" spans="1:16" ht="72.5" x14ac:dyDescent="0.35">
@@ -6301,31 +6298,31 @@
         <v>98</v>
       </c>
       <c r="B100" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="C100" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="C100" s="2" t="s">
-        <v>265</v>
-      </c>
       <c r="D100" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E100" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="J100" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L100" s="1" t="s">
         <v>11</v>
@@ -6337,10 +6334,10 @@
         <v>19</v>
       </c>
       <c r="O100" s="11" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="P100" s="11" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="101" spans="1:16" ht="58" x14ac:dyDescent="0.35">
@@ -6348,28 +6345,28 @@
         <v>99</v>
       </c>
       <c r="B101" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="C101" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="C101" s="2" t="s">
-        <v>267</v>
-      </c>
       <c r="E101" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G101" s="16" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="I101" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="J101" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L101" s="1" t="s">
         <v>11</v>
@@ -6381,10 +6378,10 @@
         <v>17</v>
       </c>
       <c r="O101" s="11" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="P101" s="11" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="102" spans="1:16" x14ac:dyDescent="0.35">
@@ -6392,28 +6389,28 @@
         <v>100</v>
       </c>
       <c r="B102" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="C102" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="C102" s="2" t="s">
-        <v>269</v>
-      </c>
       <c r="E102" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G102" s="1" t="s">
         <v>6</v>
       </c>
       <c r="J102" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L102" s="1" t="s">
         <v>12</v>
       </c>
       <c r="M102" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N102" s="1" t="s">
         <v>12</v>
@@ -6428,31 +6425,31 @@
         <v>101</v>
       </c>
       <c r="B103" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="C103" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="C103" s="2" t="s">
-        <v>271</v>
-      </c>
       <c r="E103" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="I103" s="11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="J103" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="K103" s="11" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="L103" s="1" t="s">
         <v>11</v>
@@ -6464,10 +6461,10 @@
         <v>17</v>
       </c>
       <c r="O103" s="11" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="P103" s="11" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="104" spans="1:16" ht="58" x14ac:dyDescent="0.35">
@@ -6475,34 +6472,34 @@
         <v>102</v>
       </c>
       <c r="B104" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="C104" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="C104" s="2" t="s">
+      <c r="D104" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="G104" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="D104" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="E104" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F104" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="G104" s="1" t="s">
+      <c r="H104" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="H104" s="1" t="s">
+      <c r="I104" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="J104" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="K104" s="1" t="s">
         <v>275</v>
-      </c>
-      <c r="I104" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="J104" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="K104" s="1" t="s">
-        <v>276</v>
       </c>
       <c r="L104" s="1" t="s">
         <v>11</v>
@@ -6514,10 +6511,10 @@
         <v>17</v>
       </c>
       <c r="O104" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="P104" s="11" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="105" spans="1:16" ht="58" x14ac:dyDescent="0.35">
@@ -6525,34 +6522,34 @@
         <v>103</v>
       </c>
       <c r="B105" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="C105" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="C105" s="2" t="s">
+      <c r="D105" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="G105" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="D105" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="E105" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F105" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="G105" s="1" t="s">
+      <c r="H105" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="H105" s="1" t="s">
-        <v>280</v>
-      </c>
       <c r="I105" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="J105" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="K105" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="L105" s="1" t="s">
         <v>11</v>
@@ -6564,10 +6561,10 @@
         <v>17</v>
       </c>
       <c r="O105" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="P105" s="11" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="106" spans="1:16" ht="58" x14ac:dyDescent="0.35">
@@ -6575,34 +6572,34 @@
         <v>104</v>
       </c>
       <c r="B106" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="C106" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="C106" s="2" t="s">
-        <v>282</v>
-      </c>
       <c r="D106" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E106" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G106" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="H106" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="H106" s="1" t="s">
-        <v>222</v>
-      </c>
       <c r="I106" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="J106" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="K106" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="L106" s="1" t="s">
         <v>11</v>
@@ -6614,10 +6611,10 @@
         <v>17</v>
       </c>
       <c r="O106" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="P106" s="11" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="107" spans="1:16" x14ac:dyDescent="0.35">
@@ -6625,28 +6622,28 @@
         <v>105</v>
       </c>
       <c r="B107" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="C107" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="2" t="s">
-        <v>284</v>
-      </c>
       <c r="E107" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G107" s="1" t="s">
         <v>6</v>
       </c>
       <c r="J107" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L107" s="1" t="s">
         <v>12</v>
       </c>
       <c r="M107" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N107" s="1" t="s">
         <v>12</v>
@@ -6661,28 +6658,28 @@
         <v>106</v>
       </c>
       <c r="B108" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="C108" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="C108" s="2" t="s">
-        <v>286</v>
-      </c>
       <c r="E108" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G108" s="1" t="s">
         <v>6</v>
       </c>
       <c r="J108" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L108" s="1" t="s">
         <v>12</v>
       </c>
       <c r="M108" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N108" s="1" t="s">
         <v>12</v>
@@ -6697,28 +6694,28 @@
         <v>107</v>
       </c>
       <c r="B109" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="C109" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="C109" s="2" t="s">
-        <v>288</v>
-      </c>
       <c r="E109" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G109" s="1" t="s">
         <v>6</v>
       </c>
       <c r="J109" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L109" s="1" t="s">
         <v>12</v>
       </c>
       <c r="M109" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N109" s="1" t="s">
         <v>12</v>
@@ -6733,28 +6730,28 @@
         <v>108</v>
       </c>
       <c r="B110" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="C110" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="C110" s="2" t="s">
-        <v>290</v>
-      </c>
       <c r="E110" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G110" s="1" t="s">
         <v>6</v>
       </c>
       <c r="J110" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L110" s="1" t="s">
         <v>12</v>
       </c>
       <c r="M110" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N110" s="1" t="s">
         <v>12</v>
@@ -6769,28 +6766,28 @@
         <v>109</v>
       </c>
       <c r="B111" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="C111" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="C111" s="2" t="s">
-        <v>292</v>
-      </c>
       <c r="E111" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G111" s="1" t="s">
         <v>6</v>
       </c>
       <c r="J111" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L111" s="1" t="s">
         <v>12</v>
       </c>
       <c r="M111" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N111" s="1" t="s">
         <v>12</v>
@@ -6805,28 +6802,28 @@
         <v>110</v>
       </c>
       <c r="B112" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="C112" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="C112" s="2" t="s">
-        <v>294</v>
-      </c>
       <c r="E112" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G112" s="1" t="s">
         <v>6</v>
       </c>
       <c r="J112" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L112" s="1" t="s">
         <v>12</v>
       </c>
       <c r="M112" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N112" s="1" t="s">
         <v>12</v>
@@ -6841,28 +6838,28 @@
         <v>111</v>
       </c>
       <c r="B113" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="C113" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="C113" s="2" t="s">
-        <v>296</v>
-      </c>
       <c r="E113" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G113" s="1" t="s">
         <v>6</v>
       </c>
       <c r="J113" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L113" s="1" t="s">
         <v>12</v>
       </c>
       <c r="M113" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N113" s="1" t="s">
         <v>12</v>
